--- a/verification/cases/roundtrip/formulas_financial/init.xlsx
+++ b/verification/cases/roundtrip/formulas_financial/init.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/financial/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93F99AB7-B525-7349-A3B6-7731FBCDE6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7CB43AB-4F5F-407C-B721-1366D9E05078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3320" yWindow="1860" windowWidth="29700" windowHeight="19620" xr2:uid="{CBB0D7E8-1790-9042-9BD9-D40641B90617}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CBB0D7E8-1790-9042-9BD9-D40641B90617}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -732,7 +732,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -755,30 +755,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225FE9CC-ECB3-BF4A-8D84-85FA7B167614}">
   <dimension ref="B2:H196"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="45" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
@@ -794,7 +794,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
@@ -802,7 +802,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
@@ -810,7 +810,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
@@ -818,7 +818,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
@@ -826,7 +826,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
@@ -834,7 +834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
@@ -842,7 +842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
@@ -850,7 +850,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -858,7 +858,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
@@ -866,7 +866,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
@@ -874,7 +874,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
@@ -882,7 +882,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
@@ -890,7 +890,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
@@ -898,7 +898,7 @@
         <v>-100000</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>18</v>
       </c>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
@@ -914,7 +914,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
@@ -922,7 +922,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>21</v>
       </c>
@@ -930,7 +930,7 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>22</v>
       </c>
@@ -938,7 +938,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>23</v>
       </c>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
@@ -954,7 +954,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>25</v>
       </c>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>26</v>
       </c>
@@ -970,7 +970,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>27</v>
       </c>
@@ -978,7 +978,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>28</v>
       </c>
@@ -986,7 +986,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>29</v>
       </c>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>30</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>31</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>32</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>33</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>34</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>35</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>36</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>37</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>38</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>39</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>40</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>41</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>42</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>43</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>44</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>46388</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>45</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>46</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>47</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>48</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>49</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>50</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>51</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>52</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>53</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>54</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>55</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>56</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>57</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>58</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>59</v>
       </c>
@@ -1234,15 +1234,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" s="2"/>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B64" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="14" t="s">
         <v>1</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>27.777777777777779</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -1331,7 +1331,7 @@
         <v>102.86125969255045</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B68" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -1361,7 +1361,7 @@
         <v>500.00001177124369</v>
       </c>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -1391,7 +1391,7 @@
         <v>800.00000000074226</v>
       </c>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -1421,7 +1421,7 @@
         <v>1000.0000000000014</v>
       </c>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -1451,12 +1451,12 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="14" t="s">
         <v>1</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>27.777777777777779</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -1545,7 +1545,7 @@
         <v>101.84283137876282</v>
       </c>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -1575,7 +1575,7 @@
         <v>476.19048740118444</v>
       </c>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -1605,7 +1605,7 @@
         <v>740.740740741428</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -1635,7 +1635,7 @@
         <v>909.09090909091026</v>
       </c>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -1665,12 +1665,12 @@
         <v>1304.3478260869565</v>
       </c>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="14" t="s">
         <v>1</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -1759,7 +1759,7 @@
         <v>349496.41327685065</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -1789,7 +1789,7 @@
         <v>84952790817.360458</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -1819,7 +1819,7 @@
         <v>1347292798177031.5</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -1849,7 +1849,7 @@
         <v>7.9683179881738214E+17</v>
       </c>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -1879,12 +1879,12 @@
         <v>4.7329429352723096E+24</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="14" t="s">
         <v>1</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -1943,7 +1943,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -1973,7 +1973,7 @@
         <v>712487.79068646976</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -2003,7 +2003,7 @@
         <v>513964394445.03076</v>
       </c>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -2033,7 +2033,7 @@
         <v>1.2233418607457446E+16</v>
       </c>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B97" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -2063,7 +2063,7 @@
         <v>8.8448329668729528E+18</v>
       </c>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -2093,12 +2093,12 @@
         <v>7.6437028404647796E+25</v>
       </c>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B101" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B102" s="14" t="s">
         <v>1</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B103" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -2157,7 +2157,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B104" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -2187,7 +2187,7 @@
         <v>9721.8331079064501</v>
       </c>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B105" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -2217,7 +2217,7 @@
         <v>1999.9999529150264</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B106" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -2247,7 +2247,7 @@
         <v>1249.9999999988404</v>
       </c>
     </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B107" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -2277,7 +2277,7 @@
         <v>999.99999999999864</v>
       </c>
     </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B108" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -2307,12 +2307,12 @@
         <v>666.66666666666674</v>
       </c>
     </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B110" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B111" s="14" t="s">
         <v>1</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B112" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -2371,7 +2371,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B113" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -2401,7 +2401,7 @@
         <v>9540.8845468919644</v>
       </c>
     </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B114" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -2431,7 +2431,7 @@
         <v>2099.9997151359103</v>
       </c>
     </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B115" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -2461,7 +2461,7 @@
         <v>1349.9999999894699</v>
       </c>
     </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B116" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -2491,7 +2491,7 @@
         <v>1099.9999999999861</v>
       </c>
     </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B117" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -2521,12 +2521,12 @@
         <v>766.66666666666663</v>
       </c>
     </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B120" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B121" s="14" t="s">
         <v>1</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B122" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -2558,7 +2558,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B123" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -2576,7 +2576,7 @@
         <v>274.4430035398384</v>
       </c>
     </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B124" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -2594,7 +2594,7 @@
         <v>180.42379461232713</v>
       </c>
     </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B125" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -2612,7 +2612,7 @@
         <v>117.55114866937242</v>
       </c>
     </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B126" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -2630,7 +2630,7 @@
         <v>78.819752749129066</v>
       </c>
     </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B127" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -2648,12 +2648,12 @@
         <v>-8.3297300967333285</v>
       </c>
     </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B130" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B131" s="14" t="s">
         <v>1</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B132" s="6" t="s">
         <v>67</v>
       </c>
@@ -2681,10 +2681,10 @@
       </c>
       <c r="E132" s="7">
         <f>IRR($C$47:$C$51,0.5)</f>
-        <v>0.15322137877183506</v>
-      </c>
-    </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.2">
+        <v>0.15322137877183528</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B133" s="6" t="s">
         <v>68</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>7.7138472952083648E-2</v>
       </c>
     </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B134" s="6" t="s">
         <v>69</v>
       </c>
@@ -2718,12 +2718,12 @@
         <v>0.14488844278585611</v>
       </c>
     </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B137" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B138" s="14" t="s">
         <v>1</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B139" s="8">
         <f>$C$11</f>
         <v>1</v>
@@ -2774,7 +2774,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B140" s="8">
         <f>$C$12</f>
         <v>6</v>
@@ -2800,7 +2800,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B141" s="8">
         <f>$C$13</f>
         <v>12</v>
@@ -2826,7 +2826,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B142" s="8">
         <f>$C$14</f>
         <v>24</v>
@@ -2852,7 +2852,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="143" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B143" s="8">
         <f>$C$15</f>
         <v>60</v>
@@ -2878,7 +2878,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="144" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B144" s="8">
         <f>$C$16</f>
         <v>360</v>
@@ -2904,12 +2904,12 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B147" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="148" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B148" s="14" t="s">
         <v>1</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B149" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B150" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -2986,7 +2986,7 @@
         <v>69.660716893574829</v>
       </c>
     </row>
-    <row r="151" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B151" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -3012,7 +3012,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B152" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -3038,7 +3038,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B153" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -3064,7 +3064,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B154" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -3090,12 +3090,12 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B157" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B158" s="14" t="s">
         <v>1</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B159" s="8">
         <f>$C$33</f>
         <v>10000</v>
@@ -3122,7 +3122,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="160" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B160" s="8">
         <f>$C$34</f>
         <v>50000</v>
@@ -3136,12 +3136,12 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B163" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B164" s="14" t="s">
         <v>1</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B165" s="8">
         <f>$C$39</f>
         <v>1</v>
@@ -3168,7 +3168,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B166" s="8">
         <f>$C$40</f>
         <v>2</v>
@@ -3182,7 +3182,7 @@
         <v>1635.6399999999999</v>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B167" s="8">
         <f>$C$41</f>
         <v>3</v>
@@ -3196,12 +3196,12 @@
         <v>1298.6981600000001</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B170" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B171" s="14" t="s">
         <v>1</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B172" s="8">
         <f>$C$39</f>
         <v>1</v>
@@ -3228,7 +3228,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B173" s="8">
         <f>$C$40</f>
         <v>2</v>
@@ -3242,7 +3242,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B174" s="8">
         <f>$C$41</f>
         <v>3</v>
@@ -3256,12 +3256,12 @@
         <v>1280.0000000000002</v>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B175" s="9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="176" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B176" s="14" t="s">
         <v>1</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B177" s="8">
         <f>$C$39</f>
         <v>1</v>
@@ -3288,7 +3288,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B178" s="8">
         <f>$C$40</f>
         <v>2</v>
@@ -3302,7 +3302,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B179" s="8">
         <f>$C$41</f>
         <v>3</v>
@@ -3316,12 +3316,12 @@
         <v>1083.7499999999998</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B182" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B183" s="14" t="s">
         <v>1</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B184" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B185" s="8">
         <f>$C$6</f>
         <v>0.01</v>
@@ -3371,7 +3371,7 @@
         <v>287.1758359297495</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B186" s="8">
         <f>$C$7</f>
         <v>0.05</v>
@@ -3389,7 +3389,7 @@
         <v>238.58771784228873</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B187" s="8">
         <f>$C$8</f>
         <v>0.08</v>
@@ -3407,7 +3407,7 @@
         <v>204.75801347837762</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B188" s="8">
         <f>$C$9</f>
         <v>0.1</v>
@@ -3425,7 +3425,7 @@
         <v>183.33617539326025</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B189" s="8">
         <f>$C$10</f>
         <v>0.15</v>
@@ -3443,12 +3443,12 @@
         <v>133.3626184563833</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B192" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B193" s="14" t="s">
         <v>1</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B194" s="6" t="s">
         <v>67</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>0.33071877807378769</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B195" s="6" t="s">
         <v>68</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>0.16053323820233345</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B196" s="6" t="s">
         <v>69</v>
       </c>
